--- a/台股ETF代碼.xlsx
+++ b/台股ETF代碼.xlsx
@@ -2240,8 +2240,10 @@
       <c r="A60" t="s">
         <v>167</v>
       </c>
-      <c r="B60" t="s">
-        <v>168</v>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>富邦恒生國企正2</t>
+        </is>
       </c>
       <c r="C60" t="s">
         <v>8</v>
@@ -2257,8 +2259,10 @@
       <c r="A61" t="s">
         <v>170</v>
       </c>
-      <c r="B61" t="s">
-        <v>171</v>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>富邦恒生國企反1</t>
+        </is>
       </c>
       <c r="C61" t="s">
         <v>8</v>
@@ -2767,8 +2771,10 @@
       <c r="A91" t="s">
         <v>245</v>
       </c>
-      <c r="B91" t="s">
-        <v>246</v>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>富邦恒生國企</t>
+        </is>
       </c>
       <c r="C91" t="s">
         <v>8</v>
